--- a/AppLogSolutionsWeb/Progetto Scuole/rientri_ddt.xlsx
+++ b/AppLogSolutionsWeb/Progetto Scuole/rientri_ddt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolution\dati\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolutionsWeb\Progetto Scuole\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA24CF54-45C3-4E7D-BBD8-7567CC4AB0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2084D36F-212E-4A54-A1C9-E5003F793282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="93">
   <si>
     <t>Codice consegna</t>
   </si>
@@ -241,7 +241,64 @@
     <t>p2177</t>
   </si>
   <si>
+    <t>allegato DDT 27-04-2026</t>
+  </si>
+  <si>
     <t>p2366</t>
+  </si>
+  <si>
+    <t>p8831</t>
+  </si>
+  <si>
+    <t>p8767</t>
+  </si>
+  <si>
+    <t>p13947</t>
+  </si>
+  <si>
+    <t>p2301</t>
+  </si>
+  <si>
+    <t>p1950</t>
+  </si>
+  <si>
+    <t>p2357</t>
+  </si>
+  <si>
+    <t>p2355</t>
+  </si>
+  <si>
+    <t>p2356</t>
+  </si>
+  <si>
+    <t>p6525</t>
+  </si>
+  <si>
+    <t>p8847</t>
+  </si>
+  <si>
+    <t>p2254</t>
+  </si>
+  <si>
+    <t>p1861</t>
+  </si>
+  <si>
+    <t>p2353</t>
+  </si>
+  <si>
+    <t>p2354</t>
+  </si>
+  <si>
+    <t>p1793</t>
+  </si>
+  <si>
+    <t>p13495</t>
+  </si>
+  <si>
+    <t>p2302</t>
+  </si>
+  <si>
+    <t>p1951</t>
   </si>
 </sst>
 </file>
@@ -582,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
@@ -1290,6 +1347,9 @@
       <c r="B64" s="1">
         <v>46132</v>
       </c>
+      <c r="C64" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
@@ -1298,16 +1358,187 @@
       <c r="B65" s="1">
         <v>46132</v>
       </c>
+      <c r="C65" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B66" s="1">
         <v>46132</v>
       </c>
       <c r="C66" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>10</v>
+      </c>
+      <c r="B75" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>9</v>
+      </c>
+      <c r="B77" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>83</v>
+      </c>
+      <c r="B78" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>86</v>
+      </c>
+      <c r="B81" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>87</v>
+      </c>
+      <c r="B82" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>90</v>
+      </c>
+      <c r="B85" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>91</v>
+      </c>
+      <c r="B86" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>92</v>
+      </c>
+      <c r="B87" s="1">
+        <v>46135</v>
       </c>
     </row>
   </sheetData>
